--- a/output/graficos_dimensiones/comunal_e_basneta_a_2023_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_e_basneta_a_2023_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:58</t>
+    <t xml:space="preserve">2026-09-09 23:59</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_basneta_a_2023_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_e_basneta_a_2023_coquimbo.xlsx
@@ -72,12 +72,12 @@
     <t xml:space="preserve">Vicuña</t>
   </si>
   <si>
+    <t xml:space="preserve">Paihuano</t>
+  </si>
+  <si>
     <t xml:space="preserve">La Serena</t>
   </si>
   <si>
-    <t xml:space="preserve">Paihuano</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:59</t>
+    <t xml:space="preserve">2026-09-18 10:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -738,13 +738,13 @@
         <v>18</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>4101</v>
+        <v>4105</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>93.79</v>
+        <v>94.25</v>
       </c>
     </row>
     <row r="16">
@@ -755,10 +755,14 @@
         <v>19</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>4105</v>
-      </c>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
+        <v>4101</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>93.79</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:E16"/>
